--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7903225806451613</v>
+        <v>0.8032786885245902</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4507042253521127</v>
+        <v>0.4366197183098591</v>
       </c>
       <c r="D2">
-        <v>0.6141732283464567</v>
+        <v>0.6201550387596899</v>
       </c>
       <c r="E2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
